--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT1899</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM7316-11566</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL1549608_T_WGS</t>
+          <t>AL_0000025_T_scRNA</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>GCAT</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">

--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -2573,7 +2573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2644,6 +2644,7 @@
     <col width="24" customWidth="1" min="66" max="66"/>
     <col width="24" customWidth="1" min="67" max="67"/>
     <col width="24" customWidth="1" min="68" max="68"/>
+    <col width="24" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2774,222 +2775,227 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>assay_type</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_read</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_offset</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_size</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>probe_set</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>image_type</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>slide_id</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>capture_area</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>section_thickness</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>section_depth_order</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>anatomical_region</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>orientation</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="22">
+  <dataValidations count="21">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -3005,56 +3011,53 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$30</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$9</formula1>
-    </dataValidation>
-    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$9</formula1>
+      <formula1>'Lists'!$I$2:$I$2</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$6</formula1>
+      <formula1>'Lists'!$J$2:$J$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$4</formula1>
+    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$N$2:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$O$2:$O$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$6</formula1>
+    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$4</formula1>
+    <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$R$2:$R$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BC2:BC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BG2:BG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$3</formula1>
+    <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$5</formula1>
     </dataValidation>
-    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$U$2:$U$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$V$2:$V$6</formula1>
+    <dataValidation sqref="BK2:BK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$U$2:$U$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3067,7 +3070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3108,75 +3111,70 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>spatial_barcode_read</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>spatial_barcode_read</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>image_type</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
-        <is>
-          <t>image_type</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
         <is>
           <t>capture_area</t>
         </is>
@@ -3220,32 +3218,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Complete Genomics</t>
+          <t>scRNA-Seq</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>scRNA-Seq</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Affinity Enrichment</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Affinity Enrichment</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>gex</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gex</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -3260,17 +3258,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3280,15 +3278,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>brightfield</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
-        <is>
-          <t>brightfield</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3327,27 +3320,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Illumina</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>snRNA-Seq</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Hybrid Selection</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hybrid Selection</t>
+          <t>Unstranded</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Unstranded</t>
+          <t>vdj</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vdj</t>
+          <t>index2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3362,19 +3355,19 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>index2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -3382,15 +3375,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>fluroscence_dark</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>fluroscence_dark</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -3424,27 +3412,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ion Torrent</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
           <t>Spatial Transcriptomics</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>miRNA Size Fractionation</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>miRNA Size Fractionation</t>
+          <t>First Stranded</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>First Stranded</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -3459,7 +3447,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -3467,17 +3455,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>fluroscence_colorized</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>fluroscence_colorized</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -3509,21 +3492,21 @@
           <t>SHA512</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>LS454</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PCR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PCR</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>Second Stranded</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>read2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>read2</t>
@@ -3534,17 +3517,12 @@
           <t>read2</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>read2</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>cytassist</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t>cytassist</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -3576,21 +3554,21 @@
           <t>ETag</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SOLiD</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>Not Applicable</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
@@ -3601,12 +3579,7 @@
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3628,12 +3601,7 @@
           <t>GVCF</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ONT</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3655,12 +3623,7 @@
           <t>VCF</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DNBSEQ</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3682,12 +3645,7 @@
           <t>TBI</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -2775,7 +2775,7 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">

--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1237,20 +1237,24 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1258,7 +1262,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1266,17 +1270,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1287,7 +1291,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1295,7 +1299,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1305,14 +1309,10 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "TIF", "TIFF", "BTF", "BIGTIFF", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1338,18 +1338,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "TIF", "TIFF", "BTF", "BIGTIFF", "raw"</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1357,7 +1361,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1367,30 +1371,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
+          <t>529600</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1400,10 +1400,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1411,25 +1415,25 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>MD5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -1440,7 +1444,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1448,24 +1452,20 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1481,32 +1481,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1514,32 +1514,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>"scRNA-Seq", "snRNA-Seq", "Spatial Transcriptomics"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>scRNA-Seq</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>assay_type</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1557,10 +1557,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Chemistry used to generate Visium expression signal (poly(A) capture vs targeted probe capture)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>The sequencing strategy used to generate the data file.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>"scRNA-Seq", "snRNA-Seq", "Spatial Transcriptomics"</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1568,7 +1572,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Probe_Based_GEX</t>
+          <t>scRNA-Seq</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1576,7 +1580,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>assay_type</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1586,14 +1590,10 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Specify the library modality.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>"GEX"</t>
-        </is>
-      </c>
+          <t>Chemistry used to generate Visium expression signal (poly(A) capture vs targeted probe capture)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Probe_Based_GEX</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Library selection method.</t>
+          <t>Specify the library modality.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
+          <t>"GEX"</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness.</t>
+          <t>Library selection method.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1685,10 +1685,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>The library construction method including version.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>Library strandedness.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10X V3</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1704,7 +1708,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1714,14 +1718,10 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>10x Feature Barcode Technology for cellranger-multi (molecule for insitu output)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>"gex", "vdj", "ab"</t>
-        </is>
-      </c>
+          <t>The library construction method including version.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>10X V3</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1737,28 +1737,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>10x Feature Barcode Technology for cellranger-multi (molecule for insitu output)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>"gex", "vdj", "ab"</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1766,32 +1770,28 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1809,18 +1809,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1828,7 +1832,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1838,7 +1842,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>The length of the UMI barcode sequence.</t>
+          <t>The offset in sequence of the UMI barcode.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -1849,7 +1853,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1857,7 +1861,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_read</t>
+          <t>UMI_barcode_size</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1867,22 +1871,18 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the spatial barcode.</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the UMI barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>read2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_offset</t>
+          <t>spatial_barcode_read</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1900,18 +1900,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the spatial barcode.</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>The type of read that contains the spatial barcode.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>read2</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -1919,7 +1923,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_size</t>
+          <t>spatial_barcode_offset</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1929,7 +1933,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>The length of the spatial barcode sequence.</t>
+          <t>The offset in sequence of the spatial barcode.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -1940,7 +1944,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -1948,7 +1952,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>spatial_barcode_size</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1958,22 +1962,18 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the spatial barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1991,18 +1991,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2010,7 +2014,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2020,22 +2024,18 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>The offset in sequence of the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2043,32 +2043,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If fastq/bam files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2086,10 +2086,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2105,7 +2109,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2115,7 +2119,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2126,7 +2130,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2134,7 +2138,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2144,22 +2148,18 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2177,18 +2177,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2196,7 +2200,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>probe_set</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2206,7 +2210,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Targeted probe panel used for transcript capture in probe-based spatial assays (FFPE). Not used for polyA capture spatial assays.</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2217,7 +2221,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Human_Transcriptome_Probe_Set_v1.0</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2225,17 +2229,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>probe_set</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Targeted probe panel used for transcript capture in probe-based spatial assays (FFPE). Not used for polyA capture spatial assays.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2246,7 +2250,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>Human_Transcriptome_Probe_Set_v1.0</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2254,7 +2258,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2264,22 +2268,18 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>image_type</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Type of microscopy or derived image associated with the spatial dataset.</t>
+          <t>Is the sample preserved in FFPE</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>"brightfield", "fluroscence_dark", "fluroscence_colorized", "cytassist"</t>
+          <t>"True", "False"</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>brighfield</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>slide_id</t>
+          <t>image_type</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2330,10 +2330,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Identifier of the physical spatial capture slide on which the tissue section was placed.</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Type of microscopy or derived image associated with the spatial dataset.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>"brightfield", "fluroscence_dark", "fluroscence_colorized", "cytassist"</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2341,7 +2345,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>V19J01-123</t>
+          <t>brighfield</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2349,7 +2353,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>capture_area</t>
+          <t>slide_id</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2359,14 +2363,10 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Capture area identifier on a Visium slide. Use Not Applicable if the concept doesn’t apply.</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>"A1", "B1", "C1", "D1", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Identifier of the physical spatial capture slide on which the tissue section was placed.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>V19J01-123</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2382,28 +2382,32 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>section_thickness</t>
+          <t>capture_area</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Physical thickness of the tissue section mounted on the slide. (units: µm)</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>Capture area identifier on a Visium slide. Use Not Applicable if the concept doesn’t apply.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>"A1", "B1", "C1", "D1", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2411,7 +2415,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>section_depth_order</t>
+          <t>section_thickness</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2421,18 +2425,18 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ordering of serial sections cut from the same block (1 = first/closest). Use to preserve depth relationships across sections.</t>
+          <t>Physical thickness of the tissue section mounted on the slide. (units: µm)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2440,7 +2444,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>anatomical_region</t>
+          <t>section_depth_order</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2450,18 +2454,18 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Anatomical region the section represents.</t>
+          <t>Ordering of serial sections cut from the same block (1 = first/closest). Use to preserve depth relationships across sections.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2469,7 +2473,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>orientation</t>
+          <t>anatomical_region</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Orientation of the tissue section relative to anatomical axes of the organism.</t>
+          <t>Anatomical region the section represents.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2490,7 +2494,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>anterior-posterior</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2498,17 +2502,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>orientation</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
+          <t>Orientation of the tissue section relative to anatomical axes of the organism.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2519,19 +2523,15 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>anterior-posterior</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2552,17 +2552,50 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G69"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2995,7 +3028,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="21">
+  <dataValidations count="23">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -3011,53 +3044,59 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$8</formula1>
+    </dataValidation>
     <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$30</formula1>
+      <formula1>'Lists'!$G$2:$G$30</formula1>
     </dataValidation>
     <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$6</formula1>
+      <formula1>'Lists'!$H$2:$H$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$9</formula1>
     </dataValidation>
     <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$4</formula1>
+      <formula1>'Lists'!$J$2:$J$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$2</formula1>
+      <formula1>'Lists'!$K$2:$K$2</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$9</formula1>
+      <formula1>'Lists'!$L$2:$L$9</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$6</formula1>
+      <formula1>'Lists'!$M$2:$M$6</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$4</formula1>
+      <formula1>'Lists'!$N$2:$N$4</formula1>
     </dataValidation>
     <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$6</formula1>
+      <formula1>'Lists'!$O$2:$O$6</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$6</formula1>
+      <formula1>'Lists'!$P$2:$P$6</formula1>
     </dataValidation>
     <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$6</formula1>
+      <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
     <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$4</formula1>
+      <formula1>'Lists'!$R$2:$R$4</formula1>
     </dataValidation>
     <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$Q$2:$Q$4</formula1>
+      <formula1>'Lists'!$S$2:$S$4</formula1>
     </dataValidation>
     <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$3</formula1>
+      <formula1>'Lists'!$T$2:$T$3</formula1>
     </dataValidation>
     <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$S$2:$S$3</formula1>
+      <formula1>'Lists'!$U$2:$U$3</formula1>
     </dataValidation>
     <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$V$2:$V$5</formula1>
     </dataValidation>
     <dataValidation sqref="BK2:BK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$U$2:$U$6</formula1>
+      <formula1>'Lists'!$W$2:$W$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3070,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3101,80 +3140,90 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>spatial_barcode_read</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>image_type</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>capture_area</t>
         </is>
@@ -3208,80 +3257,90 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Complete Genomics</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>scRNA-Seq</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>brightfield</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3310,75 +3369,85 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>snRNA-Seq</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>vdj</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>fluroscence_dark</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -3402,65 +3471,75 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ion Torrent</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Spatial Transcriptomics</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>fluroscence_colorized</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -3484,45 +3563,55 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LS454</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>cytassist</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -3546,40 +3635,50 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SOLiD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3598,10 +3697,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>sra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ONT</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3620,10 +3729,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DNBSEQ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3640,12 +3759,17 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -3662,7 +3786,7 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
@@ -3679,7 +3803,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -3696,7 +3820,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -3713,7 +3837,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -3730,7 +3854,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -3742,7 +3866,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -3754,7 +3878,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -3766,7 +3890,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -3778,7 +3902,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -3790,7 +3914,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -3802,77 +3926,77 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>TIF</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>TIFF</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>BTF</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>BIGTIFF</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -761,20 +761,24 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>spatial_unit</t>
+          <t>reported_gender</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Physical capture element that one barcode represents, defined by the assay technology.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -782,7 +786,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -790,7 +794,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>sample_type</t>
+          <t>spatial_unit</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -800,14 +804,10 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Text term that represents a description of the kind of tissue collected with respect to disease status</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
-        </is>
-      </c>
+          <t>Physical capture element that one barcode represents, defined by the assay technology.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -815,7 +815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>spot</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tumor_descriptor</t>
+          <t>sample_type</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
+          <t>Text term that represents a description of the kind of tissue collected with respect to disease status</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
+          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -856,7 +856,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>tumor_descriptor</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tissue type the collected sample comes from</t>
+          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Bone Marrow</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -889,20 +889,24 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>bio_replicate</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Label identifying the biological replicate this sample represents</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Tissue type the collected sample comes from</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -910,7 +914,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Rep1</t>
+          <t>Bone Marrow</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -918,7 +922,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>dose_1</t>
+          <t>bio_replicate</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -928,7 +932,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
+          <t>Label identifying the biological replicate this sample represents</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -939,7 +943,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10 nM</t>
+          <t>Rep1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -947,7 +951,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>dose_2</t>
+          <t>dose_1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
+          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -968,7 +972,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20 nM</t>
+          <t>10 nM</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -976,7 +980,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>treatment_1</t>
+          <t>dose_2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -986,7 +990,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -997,7 +1001,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>temozolomide</t>
+          <t>20 nM</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1005,7 +1009,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>treatment_2</t>
+          <t>treatment_1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1015,7 +1019,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1026,7 +1030,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>temozolomide</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1034,7 +1038,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>cell_line_composition</t>
+          <t>treatment_2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>DMEM/F12</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1063,7 +1067,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>cell_line_passage</t>
+          <t>cell_line_composition</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1073,18 +1077,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>DMEM/F12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1092,7 +1096,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>timepoint</t>
+          <t>cell_line_passage</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1102,18 +1106,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Timepoint associated with the treatment, collection, or experiment</t>
+          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24h</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1121,7 +1125,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>parental_model_id</t>
+          <t>timepoint</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
+          <t>Timepoint associated with the treatment, collection, or experiment</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1142,7 +1146,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760</t>
+          <t>24h</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1150,7 +1154,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>model_id</t>
+          <t>parental_model_id</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
+          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760-mCherry-Luciferase</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1179,7 +1183,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>local_dir_path</t>
+          <t>model_id</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
+          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1200,7 +1204,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1208,7 +1212,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>aws_s3_path</t>
+          <t>local_dir_path</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1229,7 +1233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>s3://bucket/prefix</t>
+          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1237,24 +1241,20 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_source_platform</t>
+          <t>aws_s3_path</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Source platform where files are stored and from which they are harmonized</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
-        </is>
-      </c>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>bti_aws</t>
+          <t>s3://bucket/prefix</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1270,20 +1270,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1299,17 +1303,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1328,7 +1332,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1338,14 +1342,10 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "TIF", "TIFF", "BTF", "BIGTIFF", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1371,18 +1371,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "TIF", "TIFF", "BTF", "BIGTIFF", "raw"</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1390,7 +1394,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1400,30 +1404,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t>529600</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1433,10 +1433,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1444,25 +1448,25 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
+          <t>MD5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -1473,7 +1477,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1481,24 +1485,20 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>instrument_platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1514,32 +1514,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1547,32 +1547,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>"scRNA-Seq", "snRNA-Seq", "Spatial Transcriptomics"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>scRNA-Seq</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>assay_type</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1590,10 +1590,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Chemistry used to generate Visium expression signal (poly(A) capture vs targeted probe capture)</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>The sequencing strategy used to generate the data file.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>"scRNA-Seq", "snRNA-Seq", "Spatial Transcriptomics"</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Probe_Based_GEX</t>
+          <t>scRNA-Seq</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1609,7 +1613,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>assay_type</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1619,14 +1623,10 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Specify the library modality.</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>"GEX"</t>
-        </is>
-      </c>
+          <t>Chemistry used to generate Visium expression signal (poly(A) capture vs targeted probe capture)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Probe_Based_GEX</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Library selection method.</t>
+          <t>Specify the library modality.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
+          <t>"GEX"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness.</t>
+          <t>Library selection method.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1718,10 +1718,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>The library construction method including version.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Library strandedness.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10X V3</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1737,7 +1741,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1747,14 +1751,10 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>10x Feature Barcode Technology for cellranger-multi (molecule for insitu output)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>"gex", "vdj", "ab"</t>
-        </is>
-      </c>
+          <t>The library construction method including version.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>10X V3</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1770,28 +1770,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>10x Feature Barcode Technology for cellranger-multi (molecule for insitu output)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"gex", "vdj", "ab"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1799,32 +1803,28 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1842,18 +1842,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1861,7 +1865,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1871,7 +1875,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>The length of the UMI barcode sequence.</t>
+          <t>The offset in sequence of the UMI barcode.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -1882,7 +1886,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1890,7 +1894,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_read</t>
+          <t>UMI_barcode_size</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1900,22 +1904,18 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the spatial barcode.</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the UMI barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>read2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_offset</t>
+          <t>spatial_barcode_read</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1933,18 +1933,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the spatial barcode.</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>The type of read that contains the spatial barcode.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>read2</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -1952,7 +1956,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>spatial_barcode_size</t>
+          <t>spatial_barcode_offset</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1962,7 +1966,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The length of the spatial barcode sequence.</t>
+          <t>The offset in sequence of the spatial barcode.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -1973,7 +1977,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -1981,7 +1985,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>spatial_barcode_size</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1991,22 +1995,18 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the spatial barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2024,18 +2024,22 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2043,7 +2047,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2053,22 +2057,18 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>The offset in sequence of the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2076,32 +2076,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If fastq/bam files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2119,10 +2119,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2130,7 +2134,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2138,7 +2142,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2148,7 +2152,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2159,7 +2163,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2167,7 +2171,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2177,22 +2181,18 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2210,18 +2210,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2229,7 +2233,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>probe_set</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2239,7 +2243,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Targeted probe panel used for transcript capture in probe-based spatial assays (FFPE). Not used for polyA capture spatial assays.</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2250,7 +2254,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Human_Transcriptome_Probe_Set_v1.0</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2258,17 +2262,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>probe_set</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Targeted probe panel used for transcript capture in probe-based spatial assays (FFPE). Not used for polyA capture spatial assays.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2279,7 +2283,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>Human_Transcriptome_Probe_Set_v1.0</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2287,7 +2291,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2297,22 +2301,18 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>image_type</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2330,22 +2330,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Type of microscopy or derived image associated with the spatial dataset.</t>
+          <t>Is the sample preserved in FFPE</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>"brightfield", "fluroscence_dark", "fluroscence_colorized", "cytassist"</t>
+          <t>"True", "False"</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>brighfield</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>slide_id</t>
+          <t>image_type</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2363,10 +2363,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Identifier of the physical spatial capture slide on which the tissue section was placed.</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Type of microscopy or derived image associated with the spatial dataset.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>"brightfield", "fluroscence_dark", "fluroscence_colorized", "cytassist"</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>V19J01-123</t>
+          <t>brighfield</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2382,7 +2386,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>capture_area</t>
+          <t>slide_id</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2392,14 +2396,10 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Capture area identifier on a Visium slide. Use Not Applicable if the concept doesn’t apply.</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>"A1", "B1", "C1", "D1", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Identifier of the physical spatial capture slide on which the tissue section was placed.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>V19J01-123</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2415,28 +2415,32 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>section_thickness</t>
+          <t>capture_area</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Physical thickness of the tissue section mounted on the slide. (units: µm)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Capture area identifier on a Visium slide. Use Not Applicable if the concept doesn’t apply.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>"A1", "B1", "C1", "D1", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2444,7 +2448,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>section_depth_order</t>
+          <t>section_thickness</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2454,18 +2458,18 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Ordering of serial sections cut from the same block (1 = first/closest). Use to preserve depth relationships across sections.</t>
+          <t>Physical thickness of the tissue section mounted on the slide. (units: µm)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2473,7 +2477,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>anatomical_region</t>
+          <t>section_depth_order</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2483,18 +2487,18 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Anatomical region the section represents.</t>
+          <t>Ordering of serial sections cut from the same block (1 = first/closest). Use to preserve depth relationships across sections.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2502,7 +2506,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>orientation</t>
+          <t>anatomical_region</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Orientation of the tissue section relative to anatomical axes of the organism.</t>
+          <t>Anatomical region the section represents.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2523,7 +2527,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>anterior-posterior</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -2531,17 +2535,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>orientation</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
+          <t>Orientation of the tissue section relative to anatomical axes of the organism.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2552,19 +2556,15 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>anterior-posterior</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2585,17 +2585,50 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2606,7 +2639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ1"/>
+  <dimension ref="A1:BR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2678,6 +2711,7 @@
     <col width="24" customWidth="1" min="67" max="67"/>
     <col width="24" customWidth="1" min="68" max="68"/>
     <col width="24" customWidth="1" min="69" max="69"/>
+    <col width="24" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2728,375 +2762,383 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>spatial_unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>bio_replicate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dose_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dose_2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>treatment_1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>treatment_2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>cell_line_composition</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>cell_line_passage</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>parental_model_id</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>model_id</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>local_dir_path</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>aws_s3_path</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>assay_type</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_read</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_offset</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>spatial_barcode_size</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>probe_set</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>image_type</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>slide_id</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>capture_area</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>section_thickness</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>section_depth_order</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>anatomical_region</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>orientation</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="23">
+  <dataValidations count="24">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$B$2:$B$2</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$6</formula1>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$14</formula1>
+      <formula1>'Lists'!$D$2:$D$6</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$20</formula1>
+      <formula1>'Lists'!$E$2:$E$14</formula1>
     </dataValidation>
-    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$8</formula1>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$30</formula1>
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$8</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$6</formula1>
+    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$30</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$9</formula1>
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$4</formula1>
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$2</formula1>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$9</formula1>
+      <formula1>'Lists'!$L$2:$L$2</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$6</formula1>
+      <formula1>'Lists'!$M$2:$M$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$4</formula1>
+    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$N$2:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$6</formula1>
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$O$2:$O$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$P$2:$P$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$4</formula1>
+    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$R$2:$R$6</formula1>
     </dataValidation>
     <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$3</formula1>
+    <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$U$2:$U$3</formula1>
     </dataValidation>
     <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$V$2:$V$5</formula1>
+      <formula1>'Lists'!$V$2:$V$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BK2:BK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$W$2:$W$6</formula1>
+    <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$W$2:$W$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="BL2:BL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$X$2:$X$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3109,7 +3151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3125,105 +3167,110 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>spatial_barcode_read</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>image_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>capture_area</t>
         </is>
@@ -3242,94 +3289,94 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Deceased</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Bone Marrow</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>bti_aws</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Complete Genomics</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>scRNA-Seq</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>True</t>
@@ -3337,10 +3384,15 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>brightfield</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3354,100 +3406,105 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Initial CNS Tumor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Buffy Coat</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>local_drive</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Illumina</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>snRNA-Seq</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>vdj</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>fluroscence_dark</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -3456,547 +3513,552 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
+          <t>Not Reported</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Virus-infected</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Metastatic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Derived Cell Line</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>bti_aws_and_local_drive</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Ion Torrent</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Spatial Transcriptomics</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>fluroscence_colorized</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Post-treatment</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>cgc</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>LS454</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>cytassist</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Primary Tumor</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>kids_first</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SOLiD</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Progressive</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Patient Derived Xenograft</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>sra</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>ONT</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Progressive Disease Post-Mortem</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Xenograft</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>synapse</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DNBSEQ</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Recurrence</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Relapse</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Second Malignancy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Saliva</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>TIF</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>TIFF</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>BTF</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>BIGTIFF</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_spatial_manifest_template.xlsx
+++ b/excel_templates/single_cell_spatial_manifest_template.xlsx
@@ -2296,12 +2296,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
